--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8E63B0-E3DE-49C1-93B6-20C0690B92AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361E225F-8383-455B-8EFB-290BD3DA7DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="56">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -306,6 +306,14 @@
   </si>
   <si>
     <t>三代目</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NiziU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BUMP OF CHICKEN</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1891,16 +1899,48 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="3"/>
+      <c r="A107" s="3">
+        <v>46179</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" s="3"/>
+      <c r="A108" s="3">
+        <v>46180</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="3"/>
+      <c r="A109" s="3">
+        <v>46410</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110" s="3"/>
+      <c r="A110" s="3">
+        <v>46411</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361E225F-8383-455B-8EFB-290BD3DA7DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9749B72C-CE24-4ECF-AF01-4A43A2F8E5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="60">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -314,6 +314,25 @@
   </si>
   <si>
     <t>BUMP OF CHICKEN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関西コレクション</t>
+    <rPh sb="0" eb="2">
+      <t>カンサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JO1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山田涼介</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福山雅治</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1943,57 +1962,113 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" s="3"/>
+      <c r="A111" s="3">
+        <v>46117</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="3"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="3"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="3"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="3"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="3"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="3"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="3">
+        <v>46134</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="3">
+        <v>46135</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="3">
+        <v>46201</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="3">
+        <v>46256</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="3">
+        <v>46257</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="3"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.55000000000000004">

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9749B72C-CE24-4ECF-AF01-4A43A2F8E5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABDFCD1-B284-482C-83AD-72E8850ED159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="61">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -333,6 +333,10 @@
   </si>
   <si>
     <t>福山雅治</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MAMA AWARDS</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2039,10 +2043,26 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="3"/>
+      <c r="A118" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" s="3"/>
+      <c r="A119" s="3">
+        <v>46347</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABDFCD1-B284-482C-83AD-72E8850ED159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3052F9B-2FE3-437E-8E91-6BA6AEE24C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="61">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -2065,10 +2065,26 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" s="3"/>
+      <c r="A120" s="3">
+        <v>46361</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" s="3"/>
+      <c r="A121" s="3">
+        <v>46362</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3052F9B-2FE3-437E-8E91-6BA6AEE24C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D84D964-2119-4EA5-AB0A-09706C6EF5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="62">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -337,6 +337,10 @@
   </si>
   <si>
     <t>MAMA AWARDS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BABYMONSTER</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2087,16 +2091,48 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="3"/>
+      <c r="A122" s="3">
+        <v>46437</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C122" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" s="3"/>
+      <c r="A123" s="3">
+        <v>46438</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="3"/>
+      <c r="A124" s="3">
+        <v>46287</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" s="3"/>
+      <c r="A125" s="3">
+        <v>46288</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D84D964-2119-4EA5-AB0A-09706C6EF5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2449873-770C-48D8-B149-DA8F6B231384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="63">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -341,6 +341,10 @@
   </si>
   <si>
     <t>BABYMONSTER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INI</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2135,10 +2139,26 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="3"/>
+      <c r="A126" s="3">
+        <v>46340</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" s="3"/>
+      <c r="A127" s="3">
+        <v>46341</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2449873-770C-48D8-B149-DA8F6B231384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E00527C-F1D2-460B-960A-511349695DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="65">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -345,6 +345,17 @@
   </si>
   <si>
     <t>INI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOMOTO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天神祭り</t>
+    <rPh sb="0" eb="3">
+      <t>テンジンマツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2161,54 +2172,86 @@
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" s="3"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" s="3"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130" s="3"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131" s="3"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C130" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="3">
+        <v>46228</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C131" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="3"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="3"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="3"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="3"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="3"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="3"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="3"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="3"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="3"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.55000000000000004">

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E00527C-F1D2-460B-960A-511349695DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDE7E7D-F826-44FC-9A03-C2397927DF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="66">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -356,6 +356,10 @@
     <rPh sb="0" eb="3">
       <t>テンジンマツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SixTONES</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2216,10 +2220,26 @@
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" s="3"/>
+      <c r="A132" s="3">
+        <v>46333</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133" s="3"/>
+      <c r="A133" s="3">
+        <v>46334</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDE7E7D-F826-44FC-9A03-C2397927DF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA2B315-44AE-438C-905D-881213EF21AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="68">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -360,6 +360,14 @@
   </si>
   <si>
     <t>SixTONES</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Da-ICE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RIZIN</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2242,16 +2250,48 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134" s="3"/>
+      <c r="A134" s="3">
+        <v>46431</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A135" s="3"/>
+      <c r="A135" s="3">
+        <v>46432</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136" s="3"/>
+      <c r="A136" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137" s="3"/>
+      <c r="A137" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C137" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA2B315-44AE-438C-905D-881213EF21AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11E6127-F1F2-4D7E-A809-52BA03CF76C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="69">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -368,6 +368,10 @@
   </si>
   <si>
     <t>RIZIN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BIGBANG</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2294,13 +2298,37 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A138" s="3"/>
+      <c r="A138" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A139" s="3"/>
+      <c r="A139" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A140" s="3"/>
+      <c r="A140" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11E6127-F1F2-4D7E-A809-52BA03CF76C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669AD63D-F94C-4D1B-8D23-CD83423C2FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="71">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -372,6 +372,14 @@
   </si>
   <si>
     <t>BIGBANG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブルーノマーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stray Kids</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2331,16 +2339,48 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A141" s="3"/>
+      <c r="A141" s="3">
+        <v>46406</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C141" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A142" s="3"/>
+      <c r="A142" s="3">
+        <v>46407</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C142" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143" s="3"/>
+      <c r="A143" s="3">
+        <v>46284</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144" s="3"/>
+      <c r="A144" s="3">
+        <v>46285</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669AD63D-F94C-4D1B-8D23-CD83423C2FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BBED18-5AA1-4417-9CE1-69109C66C07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="72">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -380,6 +380,16 @@
   </si>
   <si>
     <t>Stray Kids</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上方BOYS（万博）</t>
+    <rPh sb="0" eb="2">
+      <t>カミガタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バンパク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2382,52 +2392,68 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" s="3"/>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A146" s="3"/>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" s="3">
+        <v>46326</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C145" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" s="3">
+        <v>46327</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C146" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="3"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="3"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="3"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="3"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="3"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="3"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="3"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="3"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="3"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="3"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="3"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="3"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="3"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="3"/>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.55000000000000004">

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BBED18-5AA1-4417-9CE1-69109C66C07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959D28ED-8178-49FB-BF2A-37989E2E25BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="72">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -2415,10 +2415,26 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A147" s="3"/>
+      <c r="A147" s="3">
+        <v>46326</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C147" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A148" s="3"/>
+      <c r="A148" s="3">
+        <v>46327</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C148" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959D28ED-8178-49FB-BF2A-37989E2E25BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B652AB0C-876C-46AA-B8AC-E8166246A015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="73">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -390,6 +390,10 @@
     <rPh sb="7" eb="9">
       <t>バンパク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>King Gnu</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2437,10 +2441,26 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A149" s="3"/>
+      <c r="A149" s="3">
+        <v>46460</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A150" s="3"/>
+      <c r="A150" s="3">
+        <v>46461</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B652AB0C-876C-46AA-B8AC-E8166246A015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D0A884-74B8-41F2-9D13-272F510222EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="74">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -383,7 +383,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>上方BOYS（万博）</t>
+    <t>King Gnu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>XG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上方BOYS@万博</t>
     <rPh sb="0" eb="2">
       <t>カミガタ</t>
     </rPh>
@@ -392,16 +400,12 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
-  <si>
-    <t>King Gnu</t>
-    <phoneticPr fontId="1"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,6 +449,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -463,12 +476,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -490,8 +506,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2403,8 +2423,8 @@
       <c r="B145" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C145" t="s">
-        <v>71</v>
+      <c r="C145" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2414,8 +2434,8 @@
       <c r="B146" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C146" t="s">
-        <v>71</v>
+      <c r="C146" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2448,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="C149" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2459,14 +2479,30 @@
         <v>2</v>
       </c>
       <c r="C150" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" s="3">
+        <v>46445</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A151" s="3"/>
-    </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A152" s="3"/>
+      <c r="A152" s="3">
+        <v>46446</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="3"/>
@@ -2674,7 +2710,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C145" r:id="rId1" xr:uid="{092F07CB-4BA0-4F86-9AA2-647AD246034B}"/>
+    <hyperlink ref="C146" r:id="rId2" xr:uid="{06B5A1A4-B303-4723-814A-C853C1594687}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D0A884-74B8-41F2-9D13-272F510222EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE078770-51A5-4F79-9CCA-426CAA05E6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="74">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -2505,16 +2505,48 @@
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A153" s="3"/>
+      <c r="A153" s="3">
+        <v>46391</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A154" s="3"/>
+      <c r="A154" s="3">
+        <v>46392</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C154" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A155" s="3"/>
+      <c r="A155" s="3">
+        <v>46393</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A156" s="3"/>
+      <c r="A156" s="3">
+        <v>46394</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C156" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE078770-51A5-4F79-9CCA-426CAA05E6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71775004-ACC9-4568-9AAF-BE4BAACF5E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -391,11 +391,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>上方BOYS@万博</t>
+    <t>上方/万博</t>
     <rPh sb="0" eb="2">
       <t>カミガタ</t>
     </rPh>
-    <rPh sb="7" eb="9">
+    <rPh sb="3" eb="5">
       <t>バンパク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2743,8 +2743,8 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C145" r:id="rId1" xr:uid="{092F07CB-4BA0-4F86-9AA2-647AD246034B}"/>
-    <hyperlink ref="C146" r:id="rId2" xr:uid="{06B5A1A4-B303-4723-814A-C853C1594687}"/>
+    <hyperlink ref="C145" r:id="rId1" display="上方BOYS@万博" xr:uid="{092F07CB-4BA0-4F86-9AA2-647AD246034B}"/>
+    <hyperlink ref="C146" r:id="rId2" display="上方BOYS@万博" xr:uid="{06B5A1A4-B303-4723-814A-C853C1594687}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71775004-ACC9-4568-9AAF-BE4BAACF5E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6883F326-0196-4E17-A6CF-8A5A37FFE13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -405,7 +405,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,15 +449,6 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -476,11 +467,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -506,12 +494,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2742,11 +2729,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="C145" r:id="rId1" display="上方BOYS@万博" xr:uid="{092F07CB-4BA0-4F86-9AA2-647AD246034B}"/>
-    <hyperlink ref="C146" r:id="rId2" display="上方BOYS@万博" xr:uid="{06B5A1A4-B303-4723-814A-C853C1594687}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6883F326-0196-4E17-A6CF-8A5A37FFE13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A34490-FDCB-4500-9A7C-E1465D4101DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="75">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -397,6 +397,13 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>バンパク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三代目</t>
+    <rPh sb="0" eb="3">
+      <t>サンダイメ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2433,7 +2440,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2444,7 +2451,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A34490-FDCB-4500-9A7C-E1465D4101DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E325C1EF-FB2A-47E5-AB81-A5FEAF7599BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="76">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -407,12 +407,16 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t xml:space="preserve">Number_i </t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +457,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -501,7 +512,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2417,7 +2428,7 @@
       <c r="B145" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="C145" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2428,7 +2439,7 @@
       <c r="B146" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="C146" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2542,8 +2553,16 @@
         <v>39</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A157" s="3"/>
+    <row r="157" spans="1:3" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" s="3">
+        <v>46358</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E325C1EF-FB2A-47E5-AB81-A5FEAF7599BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CDBCA1-00C9-4544-8A01-835EF11829A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1380" windowWidth="29040" windowHeight="15720" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="77">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -409,6 +409,10 @@
   </si>
   <si>
     <t xml:space="preserve">Number_i </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LE SSERAFIM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2565,10 +2569,26 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A158" s="3"/>
+      <c r="A158" s="3">
+        <v>46375</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C158" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A159" s="3"/>
+      <c r="A159" s="3">
+        <v>46376</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="3"/>
